--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T14:14:01+00:00</t>
+    <t>2026-10-06T20:02:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-06T20:02:10+00:00</t>
+    <t>2026-10-07T08:37:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T08:37:44+00:00</t>
+    <t>2026-10-07T09:51:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$185</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AK$183</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5815" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5749" uniqueCount="507">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-07T09:51:04+00:00</t>
+    <t>2026-10-08T08:06:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1033,6 +1033,36 @@
     <t>templateId est optionnel. S'il est présent, son root peut être 1.2.250.1.213.1.1.3.109 et/ou une autre OID valide</t>
   </si>
   <si>
+    <t>Organizer.participant:frParticipantResponsable.templateId.nullFlavor</t>
+  </si>
+  <si>
+    <t>Organizer.participant.templateId.nullFlavor</t>
+  </si>
+  <si>
+    <t>Organizer.participant:frParticipantResponsable.templateId.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>Organizer.participant.templateId.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>Organizer.participant:frParticipantResponsable.templateId.displayable</t>
+  </si>
+  <si>
+    <t>Organizer.participant.templateId.displayable</t>
+  </si>
+  <si>
+    <t>Organizer.participant:frParticipantResponsable.templateId.root</t>
+  </si>
+  <si>
+    <t>Organizer.participant.templateId.root</t>
+  </si>
+  <si>
+    <t>Organizer.participant:frParticipantResponsable.templateId.extension</t>
+  </si>
+  <si>
+    <t>Organizer.participant.templateId.extension</t>
+  </si>
+  <si>
     <t>Organizer.participant:frParticipantResponsable.templateId:templateId</t>
   </si>
   <si>
@@ -1045,60 +1075,21 @@
     <t>Organizer.participant:frParticipantResponsable.templateId:templateId.nullFlavor</t>
   </si>
   <si>
-    <t>Organizer.participant.templateId.nullFlavor</t>
-  </si>
-  <si>
     <t>Organizer.participant:frParticipantResponsable.templateId:templateId.assigningAuthorityName</t>
   </si>
   <si>
-    <t>Organizer.participant.templateId.assigningAuthorityName</t>
-  </si>
-  <si>
     <t>Organizer.participant:frParticipantResponsable.templateId:templateId.displayable</t>
   </si>
   <si>
-    <t>Organizer.participant.templateId.displayable</t>
-  </si>
-  <si>
     <t>Organizer.participant:frParticipantResponsable.templateId:templateId.root</t>
   </si>
   <si>
-    <t>Organizer.participant.templateId.root</t>
-  </si>
-  <si>
     <t>1.2.250.1.213.1.1.3.109</t>
   </si>
   <si>
     <t>Organizer.participant:frParticipantResponsable.templateId:templateId.extension</t>
   </si>
   <si>
-    <t>Organizer.participant.templateId.extension</t>
-  </si>
-  <si>
-    <t>Organizer.participant:frParticipantResponsable.templateId:templateId-other</t>
-  </si>
-  <si>
-    <t>templateId-other</t>
-  </si>
-  <si>
-    <t>Autre TemplateId</t>
-  </si>
-  <si>
-    <t>Organizer.participant:frParticipantResponsable.templateId:templateId-other.nullFlavor</t>
-  </si>
-  <si>
-    <t>Organizer.participant:frParticipantResponsable.templateId:templateId-other.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Organizer.participant:frParticipantResponsable.templateId:templateId-other.displayable</t>
-  </si>
-  <si>
-    <t>Organizer.participant:frParticipantResponsable.templateId:templateId-other.root</t>
-  </si>
-  <si>
-    <t>Organizer.participant:frParticipantResponsable.templateId:templateId-other.extension</t>
-  </si>
-  <si>
     <t>Organizer.participant:frParticipantResponsable.typeCode</t>
   </si>
   <si>
@@ -1106,6 +1097,9 @@
   </si>
   <si>
     <t>RESP</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ParticipationType-cisis|20260916095457</t>
   </si>
   <si>
     <t>Participant2.typeCode</t>
@@ -1312,6 +1306,21 @@
     <t>Organizer.participant:frParticipantDispositif.templateId</t>
   </si>
   <si>
+    <t>Organizer.participant:frParticipantDispositif.templateId.nullFlavor</t>
+  </si>
+  <si>
+    <t>Organizer.participant:frParticipantDispositif.templateId.assigningAuthorityName</t>
+  </si>
+  <si>
+    <t>Organizer.participant:frParticipantDispositif.templateId.displayable</t>
+  </si>
+  <si>
+    <t>Organizer.participant:frParticipantDispositif.templateId.root</t>
+  </si>
+  <si>
+    <t>Organizer.participant:frParticipantDispositif.templateId.extension</t>
+  </si>
+  <si>
     <t>Organizer.participant:frParticipantDispositif.templateId:templateId</t>
   </si>
   <si>
@@ -1328,24 +1337,6 @@
   </si>
   <si>
     <t>Organizer.participant:frParticipantDispositif.templateId:templateId.extension</t>
-  </si>
-  <si>
-    <t>Organizer.participant:frParticipantDispositif.templateId:templateId-other</t>
-  </si>
-  <si>
-    <t>Organizer.participant:frParticipantDispositif.templateId:templateId-other.nullFlavor</t>
-  </si>
-  <si>
-    <t>Organizer.participant:frParticipantDispositif.templateId:templateId-other.assigningAuthorityName</t>
-  </si>
-  <si>
-    <t>Organizer.participant:frParticipantDispositif.templateId:templateId-other.displayable</t>
-  </si>
-  <si>
-    <t>Organizer.participant:frParticipantDispositif.templateId:templateId-other.root</t>
-  </si>
-  <si>
-    <t>Organizer.participant:frParticipantDispositif.templateId:templateId-other.extension</t>
   </si>
   <si>
     <t>Organizer.participant:frParticipantDispositif.typeCode</t>
@@ -1911,10 +1902,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK185"/>
+  <dimension ref="A1:AK183"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="80.64453125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="75.890625" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="71.9453125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="24.80078125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
@@ -1939,7 +1930,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="72.671875" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="73.28515625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -11907,15 +11898,15 @@
         <v>328</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="C99" t="s" s="2">
         <v>329</v>
       </c>
+      <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E99" s="2"/>
+      <c r="E99" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F99" t="s" s="2">
         <v>81</v>
       </c>
@@ -11932,13 +11923,11 @@
         <v>75</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L99" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="L99" s="2"/>
       <c r="M99" t="s" s="2">
-        <v>330</v>
+        <v>87</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -11965,13 +11954,11 @@
         <v>75</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y99" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y99" s="2"/>
       <c r="Z99" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>75</v>
@@ -11989,13 +11976,13 @@
         <v>75</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH99" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI99" t="s" s="2">
         <v>75</v>
@@ -12009,17 +11996,17 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
+        <v>330</v>
+      </c>
+      <c r="B100" t="s" s="2">
         <v>331</v>
-      </c>
-      <c r="B100" t="s" s="2">
-        <v>332</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E100" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F100" t="s" s="2">
         <v>81</v>
@@ -12037,11 +12024,11 @@
         <v>75</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L100" s="2"/>
       <c r="M100" t="s" s="2">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -12068,11 +12055,13 @@
         <v>75</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y100" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y100" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z100" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>75</v>
@@ -12090,7 +12079,7 @@
         <v>75</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -12110,17 +12099,17 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
+        <v>332</v>
+      </c>
+      <c r="B101" t="s" s="2">
         <v>333</v>
-      </c>
-      <c r="B101" t="s" s="2">
-        <v>334</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E101" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F101" t="s" s="2">
         <v>81</v>
@@ -12138,11 +12127,11 @@
         <v>75</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L101" s="2"/>
       <c r="M101" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -12193,7 +12182,7 @@
         <v>75</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -12213,20 +12202,20 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
+        <v>334</v>
+      </c>
+      <c r="B102" t="s" s="2">
         <v>335</v>
-      </c>
-      <c r="B102" t="s" s="2">
-        <v>336</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E102" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F102" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G102" t="s" s="2">
         <v>76</v>
@@ -12241,11 +12230,11 @@
         <v>75</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L102" s="2"/>
       <c r="M102" t="s" s="2">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -12296,7 +12285,7 @@
         <v>75</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -12316,20 +12305,20 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
+        <v>336</v>
+      </c>
+      <c r="B103" t="s" s="2">
         <v>337</v>
-      </c>
-      <c r="B103" t="s" s="2">
-        <v>338</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E103" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F103" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G103" t="s" s="2">
         <v>76</v>
@@ -12344,11 +12333,11 @@
         <v>75</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L103" s="2"/>
       <c r="M103" t="s" s="2">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -12360,7 +12349,7 @@
         <v>75</v>
       </c>
       <c r="S103" t="s" s="2">
-        <v>339</v>
+        <v>75</v>
       </c>
       <c r="T103" t="s" s="2">
         <v>75</v>
@@ -12399,7 +12388,7 @@
         <v>75</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -12419,39 +12408,41 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
+        <v>338</v>
+      </c>
+      <c r="B104" t="s" s="2">
+        <v>326</v>
+      </c>
+      <c r="C104" t="s" s="2">
+        <v>339</v>
+      </c>
+      <c r="D104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="E104" s="2"/>
+      <c r="F104" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="G104" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="I104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="J104" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="K104" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="L104" t="s" s="2">
         <v>340</v>
       </c>
-      <c r="B104" t="s" s="2">
-        <v>341</v>
-      </c>
-      <c r="C104" s="2"/>
-      <c r="D104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E104" t="s" s="2">
-        <v>118</v>
-      </c>
-      <c r="F104" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G104" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J104" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K104" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L104" s="2"/>
       <c r="M104" t="s" s="2">
-        <v>119</v>
+        <v>340</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -12502,13 +12493,13 @@
         <v>75</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH104" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI104" t="s" s="2">
         <v>75</v>
@@ -12522,23 +12513,23 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="C105" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>329</v>
+      </c>
+      <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E105" s="2"/>
+      <c r="E105" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G105" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H105" t="s" s="2">
         <v>75</v>
@@ -12550,13 +12541,11 @@
         <v>75</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L105" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="L105" s="2"/>
       <c r="M105" t="s" s="2">
-        <v>344</v>
+        <v>87</v>
       </c>
       <c r="N105" s="2"/>
       <c r="O105" s="2"/>
@@ -12583,13 +12572,11 @@
         <v>75</v>
       </c>
       <c r="X105" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y105" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y105" s="2"/>
       <c r="Z105" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA105" t="s" s="2">
         <v>75</v>
@@ -12607,13 +12594,13 @@
         <v>75</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH105" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI105" t="s" s="2">
         <v>75</v>
@@ -12627,17 +12614,17 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E106" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F106" t="s" s="2">
         <v>81</v>
@@ -12655,11 +12642,11 @@
         <v>75</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L106" s="2"/>
       <c r="M106" t="s" s="2">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -12686,11 +12673,13 @@
         <v>75</v>
       </c>
       <c r="X106" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y106" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y106" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z106" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA106" t="s" s="2">
         <v>75</v>
@@ -12708,7 +12697,7 @@
         <v>75</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -12728,17 +12717,17 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E107" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F107" t="s" s="2">
         <v>81</v>
@@ -12756,11 +12745,11 @@
         <v>75</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L107" s="2"/>
       <c r="M107" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -12811,7 +12800,7 @@
         <v>75</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -12831,20 +12820,20 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E108" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F108" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G108" t="s" s="2">
         <v>76</v>
@@ -12859,11 +12848,11 @@
         <v>75</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L108" s="2"/>
       <c r="M108" t="s" s="2">
-        <v>109</v>
+        <v>138</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -12875,7 +12864,7 @@
         <v>75</v>
       </c>
       <c r="S108" t="s" s="2">
-        <v>75</v>
+        <v>345</v>
       </c>
       <c r="T108" t="s" s="2">
         <v>75</v>
@@ -12914,7 +12903,7 @@
         <v>75</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -12932,28 +12921,28 @@
         <v>75</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E109" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F109" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G109" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H109" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="I109" t="s" s="2">
         <v>75</v>
@@ -12962,11 +12951,11 @@
         <v>75</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L109" s="2"/>
       <c r="M109" t="s" s="2">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" s="2"/>
@@ -13017,7 +13006,7 @@
         <v>75</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -13035,28 +13024,26 @@
         <v>75</v>
       </c>
     </row>
-    <row r="110" hidden="true">
+    <row r="110">
       <c r="A110" t="s" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>341</v>
+        <v>348</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E110" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G110" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H110" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I110" t="s" s="2">
         <v>75</v>
@@ -13065,12 +13052,10 @@
         <v>75</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="L110" s="2"/>
-      <c r="M110" t="s" s="2">
-        <v>119</v>
-      </c>
+      <c r="M110" s="2"/>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -13081,7 +13066,7 @@
         <v>75</v>
       </c>
       <c r="S110" t="s" s="2">
-        <v>75</v>
+        <v>349</v>
       </c>
       <c r="T110" t="s" s="2">
         <v>75</v>
@@ -13096,13 +13081,11 @@
         <v>75</v>
       </c>
       <c r="X110" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y110" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y110" s="2"/>
       <c r="Z110" t="s" s="2">
-        <v>75</v>
+        <v>350</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>75</v>
@@ -13120,10 +13103,10 @@
         <v>75</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>120</v>
+        <v>351</v>
       </c>
       <c r="AG110" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH110" t="s" s="2">
         <v>76</v>
@@ -13138,12 +13121,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -13151,13 +13134,13 @@
       </c>
       <c r="E111" s="2"/>
       <c r="F111" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G111" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H111" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="I111" t="s" s="2">
         <v>75</v>
@@ -13177,10 +13160,10 @@
       </c>
       <c r="Q111" s="2"/>
       <c r="R111" t="s" s="2">
-        <v>75</v>
+        <v>354</v>
       </c>
       <c r="S111" t="s" s="2">
-        <v>352</v>
+        <v>75</v>
       </c>
       <c r="T111" t="s" s="2">
         <v>75</v>
@@ -13199,7 +13182,7 @@
       </c>
       <c r="Y111" s="2"/>
       <c r="Z111" t="s" s="2">
-        <v>233</v>
+        <v>355</v>
       </c>
       <c r="AA111" t="s" s="2">
         <v>75</v>
@@ -13217,10 +13200,10 @@
         <v>75</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="AG111" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH111" t="s" s="2">
         <v>76</v>
@@ -13237,10 +13220,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -13263,7 +13246,7 @@
         <v>75</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>86</v>
+        <v>279</v>
       </c>
       <c r="L112" s="2"/>
       <c r="M112" s="2"/>
@@ -13274,7 +13257,7 @@
       </c>
       <c r="Q112" s="2"/>
       <c r="R112" t="s" s="2">
-        <v>356</v>
+        <v>75</v>
       </c>
       <c r="S112" t="s" s="2">
         <v>75</v>
@@ -13292,11 +13275,13 @@
         <v>75</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y112" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y112" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z112" t="s" s="2">
-        <v>357</v>
+        <v>75</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>75</v>
@@ -13314,7 +13299,7 @@
         <v>75</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -13332,12 +13317,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="113" hidden="true">
+    <row r="113">
       <c r="A113" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -13351,7 +13336,7 @@
         <v>76</v>
       </c>
       <c r="H113" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I113" t="s" s="2">
         <v>75</v>
@@ -13360,10 +13345,14 @@
         <v>75</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="L113" s="2"/>
-      <c r="M113" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="L113" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M113" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="N113" s="2"/>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -13413,7 +13402,7 @@
         <v>75</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>81</v>
@@ -13431,18 +13420,20 @@
         <v>75</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E114" s="2"/>
+      <c r="E114" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F114" t="s" s="2">
         <v>81</v>
       </c>
@@ -13450,7 +13441,7 @@
         <v>76</v>
       </c>
       <c r="H114" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="I114" t="s" s="2">
         <v>75</v>
@@ -13459,13 +13450,11 @@
         <v>75</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="L114" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="L114" s="2"/>
       <c r="M114" t="s" s="2">
-        <v>364</v>
+        <v>87</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -13492,13 +13481,11 @@
         <v>75</v>
       </c>
       <c r="X114" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y114" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y114" s="2"/>
       <c r="Z114" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>75</v>
@@ -13516,7 +13503,7 @@
         <v>75</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>365</v>
+        <v>90</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>81</v>
@@ -13545,9 +13532,7 @@
       <c r="D115" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E115" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
         <v>81</v>
       </c>
@@ -13564,11 +13549,11 @@
         <v>75</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>86</v>
+        <v>368</v>
       </c>
       <c r="L115" s="2"/>
       <c r="M115" t="s" s="2">
-        <v>87</v>
+        <v>369</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -13595,11 +13580,13 @@
         <v>75</v>
       </c>
       <c r="X115" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y115" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y115" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z115" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>75</v>
@@ -13617,7 +13604,7 @@
         <v>75</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>90</v>
+        <v>370</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>81</v>
@@ -13637,10 +13624,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -13663,16 +13650,16 @@
         <v>75</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>370</v>
+        <v>86</v>
       </c>
       <c r="L116" s="2"/>
       <c r="M116" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
-        <v>75</v>
+        <v>374</v>
       </c>
       <c r="Q116" s="2"/>
       <c r="R116" t="s" s="2">
@@ -13694,13 +13681,11 @@
         <v>75</v>
       </c>
       <c r="X116" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y116" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y116" s="2"/>
       <c r="Z116" t="s" s="2">
-        <v>75</v>
+        <v>375</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>75</v>
@@ -13718,7 +13703,7 @@
         <v>75</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>81</v>
@@ -13736,18 +13721,20 @@
         <v>75</v>
       </c>
     </row>
-    <row r="117" hidden="true">
+    <row r="117">
       <c r="A117" t="s" s="2">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E117" s="2"/>
+      <c r="E117" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="F117" t="s" s="2">
         <v>81</v>
       </c>
@@ -13755,7 +13742,7 @@
         <v>76</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>75</v>
@@ -13764,16 +13751,16 @@
         <v>75</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>86</v>
+        <v>380</v>
       </c>
       <c r="L117" s="2"/>
       <c r="M117" t="s" s="2">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
-        <v>376</v>
+        <v>75</v>
       </c>
       <c r="Q117" s="2"/>
       <c r="R117" t="s" s="2">
@@ -13795,11 +13782,13 @@
         <v>75</v>
       </c>
       <c r="X117" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y117" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y117" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z117" t="s" s="2">
-        <v>377</v>
+        <v>75</v>
       </c>
       <c r="AA117" t="s" s="2">
         <v>75</v>
@@ -13817,7 +13806,7 @@
         <v>75</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>81</v>
@@ -13835,19 +13824,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E118" t="s" s="2">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="F118" t="s" s="2">
         <v>81</v>
@@ -13856,7 +13845,7 @@
         <v>76</v>
       </c>
       <c r="H118" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="I118" t="s" s="2">
         <v>75</v>
@@ -13865,11 +13854,11 @@
         <v>75</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>382</v>
+        <v>289</v>
       </c>
       <c r="L118" s="2"/>
       <c r="M118" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" s="2"/>
@@ -13920,7 +13909,7 @@
         <v>75</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>81</v>
@@ -13940,17 +13929,17 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E119" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F119" t="s" s="2">
         <v>81</v>
@@ -13968,11 +13957,11 @@
         <v>75</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>289</v>
+        <v>283</v>
       </c>
       <c r="L119" s="2"/>
       <c r="M119" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" s="2"/>
@@ -14023,7 +14012,7 @@
         <v>75</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>81</v>
@@ -14041,19 +14030,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="120" hidden="true">
+    <row r="120">
       <c r="A120" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E120" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="F120" t="s" s="2">
         <v>81</v>
@@ -14062,7 +14051,7 @@
         <v>76</v>
       </c>
       <c r="H120" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I120" t="s" s="2">
         <v>75</v>
@@ -14071,11 +14060,11 @@
         <v>75</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>283</v>
+        <v>380</v>
       </c>
       <c r="L120" s="2"/>
       <c r="M120" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" s="2"/>
@@ -14126,7 +14115,7 @@
         <v>75</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>81</v>
@@ -14144,20 +14133,18 @@
         <v>75</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E121" t="s" s="2">
-        <v>397</v>
-      </c>
+      <c r="E121" s="2"/>
       <c r="F121" t="s" s="2">
         <v>81</v>
       </c>
@@ -14165,7 +14152,7 @@
         <v>76</v>
       </c>
       <c r="H121" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="I121" t="s" s="2">
         <v>75</v>
@@ -14174,12 +14161,10 @@
         <v>75</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>382</v>
+        <v>279</v>
       </c>
       <c r="L121" s="2"/>
-      <c r="M121" t="s" s="2">
-        <v>398</v>
-      </c>
+      <c r="M121" s="2"/>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -14229,7 +14214,7 @@
         <v>75</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>81</v>
@@ -14247,12 +14232,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="122" hidden="true">
+    <row r="122">
       <c r="A122" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -14260,13 +14245,13 @@
       </c>
       <c r="E122" s="2"/>
       <c r="F122" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G122" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>75</v>
@@ -14275,10 +14260,14 @@
         <v>75</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>279</v>
-      </c>
-      <c r="L122" s="2"/>
-      <c r="M122" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="L122" t="s" s="2">
+        <v>404</v>
+      </c>
+      <c r="M122" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -14328,10 +14317,10 @@
         <v>75</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="AG122" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH122" t="s" s="2">
         <v>76</v>
@@ -14346,26 +14335,28 @@
         <v>75</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="C123" s="2"/>
+        <v>302</v>
+      </c>
+      <c r="C123" t="s" s="2">
+        <v>407</v>
+      </c>
       <c r="D123" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H123" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="I123" t="s" s="2">
         <v>75</v>
@@ -14374,14 +14365,12 @@
         <v>75</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>405</v>
+        <v>307</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="M123" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>408</v>
+      </c>
+      <c r="M123" s="2"/>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
@@ -14431,13 +14420,13 @@
         <v>75</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>407</v>
+        <v>302</v>
       </c>
       <c r="AG123" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>75</v>
@@ -14451,23 +14440,23 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>302</v>
-      </c>
-      <c r="C124" t="s" s="2">
-        <v>409</v>
-      </c>
+        <v>310</v>
+      </c>
+      <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E124" s="2"/>
+      <c r="E124" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>75</v>
@@ -14479,12 +14468,12 @@
         <v>75</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>307</v>
-      </c>
-      <c r="L124" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="M124" s="2"/>
+        <v>86</v>
+      </c>
+      <c r="L124" s="2"/>
+      <c r="M124" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -14510,13 +14499,11 @@
         <v>75</v>
       </c>
       <c r="X124" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y124" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y124" s="2"/>
       <c r="Z124" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA124" t="s" s="2">
         <v>75</v>
@@ -14534,13 +14521,13 @@
         <v>75</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>302</v>
+        <v>90</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH124" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI124" t="s" s="2">
         <v>75</v>
@@ -14554,23 +14541,21 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E125" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>75</v>
@@ -14582,11 +14567,11 @@
         <v>75</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="L125" s="2"/>
       <c r="M125" t="s" s="2">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" s="2"/>
@@ -14613,11 +14598,13 @@
         <v>75</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y125" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y125" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z125" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>75</v>
@@ -14635,13 +14622,13 @@
         <v>75</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>75</v>
@@ -14655,10 +14642,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -14669,7 +14656,7 @@
         <v>81</v>
       </c>
       <c r="G126" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H126" t="s" s="2">
         <v>75</v>
@@ -14681,11 +14668,11 @@
         <v>75</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="L126" s="2"/>
       <c r="M126" t="s" s="2">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -14736,19 +14723,19 @@
         <v>75</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH126" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI126" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AJ126" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK126" t="s" s="2">
         <v>75</v>
@@ -14756,16 +14743,18 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E127" s="2"/>
+      <c r="E127" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F127" t="s" s="2">
         <v>81</v>
       </c>
@@ -14782,11 +14771,11 @@
         <v>75</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="L127" s="2"/>
       <c r="M127" t="s" s="2">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -14813,13 +14802,11 @@
         <v>75</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y127" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y127" s="2"/>
       <c r="Z127" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>75</v>
@@ -14837,7 +14824,7 @@
         <v>75</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>81</v>
@@ -14849,7 +14836,7 @@
         <v>75</v>
       </c>
       <c r="AJ127" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK127" t="s" s="2">
         <v>75</v>
@@ -14857,17 +14844,17 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E128" t="s" s="2">
-        <v>85</v>
+        <v>102</v>
       </c>
       <c r="F128" t="s" s="2">
         <v>81</v>
@@ -14885,11 +14872,11 @@
         <v>75</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="L128" s="2"/>
       <c r="M128" t="s" s="2">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -14916,11 +14903,13 @@
         <v>75</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y128" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z128" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>75</v>
@@ -14938,7 +14927,7 @@
         <v>75</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>90</v>
+        <v>105</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>81</v>
@@ -14958,17 +14947,17 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E129" t="s" s="2">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="F129" t="s" s="2">
         <v>81</v>
@@ -14986,11 +14975,11 @@
         <v>75</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="L129" s="2"/>
       <c r="M129" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" s="2"/>
@@ -15041,7 +15030,7 @@
         <v>75</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>81</v>
@@ -15061,20 +15050,20 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E130" t="s" s="2">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="F130" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G130" t="s" s="2">
         <v>76</v>
@@ -15089,11 +15078,11 @@
         <v>75</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="L130" s="2"/>
       <c r="M130" t="s" s="2">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="N130" s="2"/>
       <c r="O130" s="2"/>
@@ -15102,7 +15091,7 @@
       </c>
       <c r="Q130" s="2"/>
       <c r="R130" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S130" t="s" s="2">
         <v>75</v>
@@ -15144,7 +15133,7 @@
         <v>75</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>81</v>
@@ -15164,17 +15153,17 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E131" t="s" s="2">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="F131" t="s" s="2">
         <v>76</v>
@@ -15192,11 +15181,11 @@
         <v>75</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="L131" s="2"/>
       <c r="M131" t="s" s="2">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="N131" s="2"/>
       <c r="O131" s="2"/>
@@ -15205,7 +15194,7 @@
       </c>
       <c r="Q131" s="2"/>
       <c r="R131" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S131" t="s" s="2">
         <v>75</v>
@@ -15247,7 +15236,7 @@
         <v>75</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>81</v>
@@ -15267,23 +15256,21 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E132" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E132" s="2"/>
       <c r="F132" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G132" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H132" t="s" s="2">
         <v>75</v>
@@ -15295,11 +15282,13 @@
         <v>75</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="L132" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>327</v>
+      </c>
       <c r="M132" t="s" s="2">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" s="2"/>
@@ -15338,25 +15327,23 @@
         <v>75</v>
       </c>
       <c r="AB132" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC132" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>124</v>
+      </c>
+      <c r="AC132" s="2"/>
       <c r="AD132" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE132" t="s" s="2">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH132" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI132" t="s" s="2">
         <v>75</v>
@@ -15370,21 +15357,23 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E133" s="2"/>
+      <c r="E133" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F133" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G133" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H133" t="s" s="2">
         <v>75</v>
@@ -15396,13 +15385,11 @@
         <v>75</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L133" t="s" s="2">
-        <v>327</v>
-      </c>
+        <v>86</v>
+      </c>
+      <c r="L133" s="2"/>
       <c r="M133" t="s" s="2">
-        <v>123</v>
+        <v>87</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" s="2"/>
@@ -15429,35 +15416,35 @@
         <v>75</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y133" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y133" s="2"/>
       <c r="Z133" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AB133" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AC133" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="AC133" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="AD133" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AE133" t="s" s="2">
-        <v>125</v>
+        <v>75</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>126</v>
+        <v>90</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH133" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI133" t="s" s="2">
         <v>75</v>
@@ -15471,18 +15458,18 @@
     </row>
     <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="C134" t="s" s="2">
-        <v>329</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E134" s="2"/>
+      <c r="E134" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="F134" t="s" s="2">
         <v>81</v>
       </c>
@@ -15499,13 +15486,11 @@
         <v>75</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L134" t="s" s="2">
-        <v>330</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="L134" s="2"/>
       <c r="M134" t="s" s="2">
-        <v>330</v>
+        <v>104</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" s="2"/>
@@ -15556,13 +15541,13 @@
         <v>75</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH134" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI134" t="s" s="2">
         <v>75</v>
@@ -15576,17 +15561,17 @@
     </row>
     <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E135" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="F135" t="s" s="2">
         <v>81</v>
@@ -15604,11 +15589,11 @@
         <v>75</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="L135" s="2"/>
       <c r="M135" t="s" s="2">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" s="2"/>
@@ -15635,11 +15620,13 @@
         <v>75</v>
       </c>
       <c r="X135" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y135" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y135" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z135" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA135" t="s" s="2">
         <v>75</v>
@@ -15657,7 +15644,7 @@
         <v>75</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>81</v>
@@ -15677,20 +15664,20 @@
     </row>
     <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E136" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="F136" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G136" t="s" s="2">
         <v>76</v>
@@ -15705,11 +15692,11 @@
         <v>75</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L136" s="2"/>
       <c r="M136" t="s" s="2">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" s="2"/>
@@ -15760,7 +15747,7 @@
         <v>75</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>81</v>
@@ -15780,17 +15767,17 @@
     </row>
     <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E137" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="F137" t="s" s="2">
         <v>81</v>
@@ -15808,11 +15795,11 @@
         <v>75</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="L137" s="2"/>
       <c r="M137" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="N137" s="2"/>
       <c r="O137" s="2"/>
@@ -15863,7 +15850,7 @@
         <v>75</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>81</v>
@@ -15883,20 +15870,20 @@
     </row>
     <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>338</v>
-      </c>
-      <c r="C138" s="2"/>
+        <v>326</v>
+      </c>
+      <c r="C138" t="s" s="2">
+        <v>339</v>
+      </c>
       <c r="D138" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E138" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="E138" s="2"/>
       <c r="F138" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G138" t="s" s="2">
         <v>76</v>
@@ -15911,11 +15898,13 @@
         <v>75</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="L138" s="2"/>
+        <v>96</v>
+      </c>
+      <c r="L138" t="s" s="2">
+        <v>340</v>
+      </c>
       <c r="M138" t="s" s="2">
-        <v>138</v>
+        <v>340</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" s="2"/>
@@ -15927,7 +15916,7 @@
         <v>75</v>
       </c>
       <c r="S138" t="s" s="2">
-        <v>339</v>
+        <v>75</v>
       </c>
       <c r="T138" t="s" s="2">
         <v>75</v>
@@ -15966,13 +15955,13 @@
         <v>75</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH138" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI138" t="s" s="2">
         <v>75</v>
@@ -15986,17 +15975,17 @@
     </row>
     <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>341</v>
+        <v>329</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E139" t="s" s="2">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="F139" t="s" s="2">
         <v>81</v>
@@ -16014,11 +16003,11 @@
         <v>75</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="L139" s="2"/>
       <c r="M139" t="s" s="2">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="N139" s="2"/>
       <c r="O139" s="2"/>
@@ -16045,13 +16034,11 @@
         <v>75</v>
       </c>
       <c r="X139" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y139" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y139" s="2"/>
       <c r="Z139" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA139" t="s" s="2">
         <v>75</v>
@@ -16069,7 +16056,7 @@
         <v>75</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>81</v>
@@ -16089,23 +16076,23 @@
     </row>
     <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>326</v>
-      </c>
-      <c r="C140" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>331</v>
+      </c>
+      <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E140" s="2"/>
+      <c r="E140" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="F140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G140" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H140" t="s" s="2">
         <v>75</v>
@@ -16117,13 +16104,11 @@
         <v>75</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="L140" t="s" s="2">
-        <v>344</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="L140" s="2"/>
       <c r="M140" t="s" s="2">
-        <v>344</v>
+        <v>104</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" s="2"/>
@@ -16174,13 +16159,13 @@
         <v>75</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH140" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI140" t="s" s="2">
         <v>75</v>
@@ -16194,17 +16179,17 @@
     </row>
     <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E141" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="F141" t="s" s="2">
         <v>81</v>
@@ -16222,11 +16207,11 @@
         <v>75</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="L141" s="2"/>
       <c r="M141" t="s" s="2">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -16253,11 +16238,13 @@
         <v>75</v>
       </c>
       <c r="X141" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y141" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y141" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z141" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA141" t="s" s="2">
         <v>75</v>
@@ -16275,7 +16262,7 @@
         <v>75</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>81</v>
@@ -16295,20 +16282,20 @@
     </row>
     <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E142" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="F142" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G142" t="s" s="2">
         <v>76</v>
@@ -16323,11 +16310,11 @@
         <v>75</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L142" s="2"/>
       <c r="M142" t="s" s="2">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -16339,7 +16326,7 @@
         <v>75</v>
       </c>
       <c r="S142" t="s" s="2">
-        <v>75</v>
+        <v>345</v>
       </c>
       <c r="T142" t="s" s="2">
         <v>75</v>
@@ -16378,7 +16365,7 @@
         <v>75</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>81</v>
@@ -16398,17 +16385,17 @@
     </row>
     <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E143" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="F143" t="s" s="2">
         <v>81</v>
@@ -16426,11 +16413,11 @@
         <v>75</v>
       </c>
       <c r="K143" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="L143" s="2"/>
       <c r="M143" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="N143" s="2"/>
       <c r="O143" s="2"/>
@@ -16481,7 +16468,7 @@
         <v>75</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>81</v>
@@ -16501,18 +16488,16 @@
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E144" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
         <v>76</v>
       </c>
@@ -16529,12 +16514,10 @@
         <v>75</v>
       </c>
       <c r="K144" t="s" s="2">
-        <v>113</v>
+        <v>86</v>
       </c>
       <c r="L144" s="2"/>
-      <c r="M144" t="s" s="2">
-        <v>138</v>
-      </c>
+      <c r="M144" s="2"/>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
       <c r="P144" t="s" s="2">
@@ -16545,7 +16528,7 @@
         <v>75</v>
       </c>
       <c r="S144" t="s" s="2">
-        <v>75</v>
+        <v>430</v>
       </c>
       <c r="T144" t="s" s="2">
         <v>75</v>
@@ -16560,13 +16543,11 @@
         <v>75</v>
       </c>
       <c r="X144" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y144" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y144" s="2"/>
       <c r="Z144" t="s" s="2">
-        <v>75</v>
+        <v>350</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>75</v>
@@ -16584,10 +16565,10 @@
         <v>75</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>116</v>
+        <v>351</v>
       </c>
       <c r="AG144" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH144" t="s" s="2">
         <v>76</v>
@@ -16607,15 +16588,13 @@
         <v>431</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E145" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E145" s="2"/>
       <c r="F145" t="s" s="2">
         <v>81</v>
       </c>
@@ -16632,12 +16611,10 @@
         <v>75</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="L145" s="2"/>
-      <c r="M145" t="s" s="2">
-        <v>119</v>
-      </c>
+      <c r="M145" s="2"/>
       <c r="N145" s="2"/>
       <c r="O145" s="2"/>
       <c r="P145" t="s" s="2">
@@ -16645,7 +16622,7 @@
       </c>
       <c r="Q145" s="2"/>
       <c r="R145" t="s" s="2">
-        <v>75</v>
+        <v>354</v>
       </c>
       <c r="S145" t="s" s="2">
         <v>75</v>
@@ -16663,13 +16640,11 @@
         <v>75</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y145" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y145" s="2"/>
       <c r="Z145" t="s" s="2">
-        <v>75</v>
+        <v>355</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>75</v>
@@ -16687,7 +16662,7 @@
         <v>75</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>120</v>
+        <v>356</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>81</v>
@@ -16705,12 +16680,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
         <v>432</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>351</v>
+        <v>358</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -16718,13 +16693,13 @@
       </c>
       <c r="E146" s="2"/>
       <c r="F146" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G146" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H146" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="I146" t="s" s="2">
         <v>75</v>
@@ -16733,7 +16708,7 @@
         <v>75</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>86</v>
+        <v>279</v>
       </c>
       <c r="L146" s="2"/>
       <c r="M146" s="2"/>
@@ -16747,67 +16722,69 @@
         <v>75</v>
       </c>
       <c r="S146" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="T146" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="U146" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="V146" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="W146" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="X146" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Y146" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="Z146" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AA146" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AB146" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AC146" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AD146" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AE146" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AF146" t="s" s="2">
+        <v>359</v>
+      </c>
+      <c r="AG146" t="s" s="2">
+        <v>81</v>
+      </c>
+      <c r="AH146" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI146" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AJ146" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AK146" t="s" s="2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="T146" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U146" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V146" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W146" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X146" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y146" s="2"/>
-      <c r="Z146" t="s" s="2">
-        <v>233</v>
-      </c>
-      <c r="AA146" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB146" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC146" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD146" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE146" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF146" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AG146" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AH146" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI146" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ146" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK146" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="147" hidden="true">
-      <c r="A147" t="s" s="2">
-        <v>434</v>
-      </c>
       <c r="B147" t="s" s="2">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -16821,7 +16798,7 @@
         <v>76</v>
       </c>
       <c r="H147" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I147" t="s" s="2">
         <v>75</v>
@@ -16830,10 +16807,14 @@
         <v>75</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>86</v>
-      </c>
-      <c r="L147" s="2"/>
-      <c r="M147" s="2"/>
+        <v>214</v>
+      </c>
+      <c r="L147" t="s" s="2">
+        <v>362</v>
+      </c>
+      <c r="M147" t="s" s="2">
+        <v>362</v>
+      </c>
       <c r="N147" s="2"/>
       <c r="O147" s="2"/>
       <c r="P147" t="s" s="2">
@@ -16841,7 +16822,7 @@
       </c>
       <c r="Q147" s="2"/>
       <c r="R147" t="s" s="2">
-        <v>356</v>
+        <v>75</v>
       </c>
       <c r="S147" t="s" s="2">
         <v>75</v>
@@ -16859,11 +16840,13 @@
         <v>75</v>
       </c>
       <c r="X147" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y147" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y147" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z147" t="s" s="2">
-        <v>357</v>
+        <v>75</v>
       </c>
       <c r="AA147" t="s" s="2">
         <v>75</v>
@@ -16881,7 +16864,7 @@
         <v>75</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>81</v>
@@ -16901,16 +16884,18 @@
     </row>
     <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E148" s="2"/>
+      <c r="E148" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F148" t="s" s="2">
         <v>81</v>
       </c>
@@ -16927,10 +16912,12 @@
         <v>75</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>279</v>
+        <v>86</v>
       </c>
       <c r="L148" s="2"/>
-      <c r="M148" s="2"/>
+      <c r="M148" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N148" s="2"/>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
@@ -16956,13 +16943,11 @@
         <v>75</v>
       </c>
       <c r="X148" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y148" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y148" s="2"/>
       <c r="Z148" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA148" t="s" s="2">
         <v>75</v>
@@ -16980,7 +16965,7 @@
         <v>75</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>361</v>
+        <v>90</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>81</v>
@@ -16998,12 +16983,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -17017,7 +17002,7 @@
         <v>76</v>
       </c>
       <c r="H149" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="I149" t="s" s="2">
         <v>75</v>
@@ -17026,13 +17011,11 @@
         <v>75</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>214</v>
-      </c>
-      <c r="L149" t="s" s="2">
-        <v>364</v>
-      </c>
+        <v>368</v>
+      </c>
+      <c r="L149" s="2"/>
       <c r="M149" t="s" s="2">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -17083,7 +17066,7 @@
         <v>75</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>81</v>
@@ -17103,18 +17086,16 @@
     </row>
     <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E150" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
         <v>81</v>
       </c>
@@ -17135,12 +17116,12 @@
       </c>
       <c r="L150" s="2"/>
       <c r="M150" t="s" s="2">
-        <v>87</v>
+        <v>373</v>
       </c>
       <c r="N150" s="2"/>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
-        <v>75</v>
+        <v>374</v>
       </c>
       <c r="Q150" s="2"/>
       <c r="R150" t="s" s="2">
@@ -17166,7 +17147,7 @@
       </c>
       <c r="Y150" s="2"/>
       <c r="Z150" t="s" s="2">
-        <v>89</v>
+        <v>375</v>
       </c>
       <c r="AA150" t="s" s="2">
         <v>75</v>
@@ -17184,7 +17165,7 @@
         <v>75</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>90</v>
+        <v>376</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>81</v>
@@ -17202,18 +17183,20 @@
         <v>75</v>
       </c>
     </row>
-    <row r="151" hidden="true">
+    <row r="151">
       <c r="A151" t="s" s="2">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E151" s="2"/>
+      <c r="E151" t="s" s="2">
+        <v>379</v>
+      </c>
       <c r="F151" t="s" s="2">
         <v>81</v>
       </c>
@@ -17221,7 +17204,7 @@
         <v>76</v>
       </c>
       <c r="H151" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I151" t="s" s="2">
         <v>75</v>
@@ -17230,11 +17213,11 @@
         <v>75</v>
       </c>
       <c r="K151" t="s" s="2">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="L151" s="2"/>
       <c r="M151" t="s" s="2">
-        <v>371</v>
+        <v>381</v>
       </c>
       <c r="N151" s="2"/>
       <c r="O151" s="2"/>
@@ -17285,7 +17268,7 @@
         <v>75</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>81</v>
@@ -17305,16 +17288,18 @@
     </row>
     <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>374</v>
+        <v>384</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E152" s="2"/>
+      <c r="E152" t="s" s="2">
+        <v>385</v>
+      </c>
       <c r="F152" t="s" s="2">
         <v>81</v>
       </c>
@@ -17331,16 +17316,16 @@
         <v>75</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>86</v>
+        <v>289</v>
       </c>
       <c r="L152" s="2"/>
       <c r="M152" t="s" s="2">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" s="2"/>
       <c r="P152" t="s" s="2">
-        <v>376</v>
+        <v>75</v>
       </c>
       <c r="Q152" s="2"/>
       <c r="R152" t="s" s="2">
@@ -17362,11 +17347,13 @@
         <v>75</v>
       </c>
       <c r="X152" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y152" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y152" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z152" t="s" s="2">
-        <v>377</v>
+        <v>75</v>
       </c>
       <c r="AA152" t="s" s="2">
         <v>75</v>
@@ -17384,7 +17371,7 @@
         <v>75</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>81</v>
@@ -17402,19 +17389,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E153" t="s" s="2">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="F153" t="s" s="2">
         <v>81</v>
@@ -17423,7 +17410,7 @@
         <v>76</v>
       </c>
       <c r="H153" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="I153" t="s" s="2">
         <v>75</v>
@@ -17432,11 +17419,11 @@
         <v>75</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>382</v>
+        <v>283</v>
       </c>
       <c r="L153" s="2"/>
       <c r="M153" t="s" s="2">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" s="2"/>
@@ -17487,7 +17474,7 @@
         <v>75</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>81</v>
@@ -17505,19 +17492,19 @@
         <v>75</v>
       </c>
     </row>
-    <row r="154" hidden="true">
+    <row r="154">
       <c r="A154" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E154" t="s" s="2">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="F154" t="s" s="2">
         <v>81</v>
@@ -17526,7 +17513,7 @@
         <v>76</v>
       </c>
       <c r="H154" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I154" t="s" s="2">
         <v>75</v>
@@ -17535,11 +17522,11 @@
         <v>75</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>289</v>
+        <v>380</v>
       </c>
       <c r="L154" s="2"/>
       <c r="M154" t="s" s="2">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" s="2"/>
@@ -17590,7 +17577,7 @@
         <v>75</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>81</v>
@@ -17610,18 +17597,16 @@
     </row>
     <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E155" t="s" s="2">
-        <v>392</v>
-      </c>
+      <c r="E155" s="2"/>
       <c r="F155" t="s" s="2">
         <v>81</v>
       </c>
@@ -17638,12 +17623,10 @@
         <v>75</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="L155" s="2"/>
-      <c r="M155" t="s" s="2">
-        <v>393</v>
-      </c>
+      <c r="M155" s="2"/>
       <c r="N155" s="2"/>
       <c r="O155" s="2"/>
       <c r="P155" t="s" s="2">
@@ -17693,7 +17676,7 @@
         <v>75</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>81</v>
@@ -17713,20 +17696,18 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E156" t="s" s="2">
-        <v>397</v>
-      </c>
+      <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G156" t="s" s="2">
         <v>76</v>
@@ -17741,11 +17722,13 @@
         <v>75</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="L156" s="2"/>
+        <v>403</v>
+      </c>
+      <c r="L156" t="s" s="2">
+        <v>404</v>
+      </c>
       <c r="M156" t="s" s="2">
-        <v>398</v>
+        <v>404</v>
       </c>
       <c r="N156" s="2"/>
       <c r="O156" s="2"/>
@@ -17796,10 +17779,10 @@
         <v>75</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>399</v>
+        <v>405</v>
       </c>
       <c r="AG156" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="AH156" t="s" s="2">
         <v>76</v>
@@ -17816,10 +17799,10 @@
     </row>
     <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>401</v>
+        <v>443</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
@@ -17830,7 +17813,7 @@
         <v>81</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>75</v>
@@ -17842,7 +17825,7 @@
         <v>75</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>279</v>
+        <v>444</v>
       </c>
       <c r="L157" s="2"/>
       <c r="M157" s="2"/>
@@ -17895,13 +17878,13 @@
         <v>75</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>402</v>
+        <v>443</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH157" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI157" t="s" s="2">
         <v>75</v>
@@ -17913,12 +17896,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
         <v>445</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>404</v>
+        <v>445</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -17926,13 +17909,13 @@
       </c>
       <c r="E158" s="2"/>
       <c r="F158" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G158" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H158" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="I158" t="s" s="2">
         <v>75</v>
@@ -17941,14 +17924,10 @@
         <v>75</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="L158" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="M158" t="s" s="2">
-        <v>406</v>
-      </c>
+        <v>446</v>
+      </c>
+      <c r="L158" s="2"/>
+      <c r="M158" s="2"/>
       <c r="N158" s="2"/>
       <c r="O158" s="2"/>
       <c r="P158" t="s" s="2">
@@ -17998,13 +17977,13 @@
         <v>75</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>407</v>
+        <v>445</v>
       </c>
       <c r="AG158" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AH158" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI158" t="s" s="2">
         <v>75</v>
@@ -18018,10 +17997,10 @@
     </row>
     <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -18044,7 +18023,7 @@
         <v>75</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="L159" s="2"/>
       <c r="M159" s="2"/>
@@ -18097,7 +18076,7 @@
         <v>75</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>81</v>
@@ -18115,12 +18094,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="160" hidden="true">
+    <row r="160">
       <c r="A160" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -18134,7 +18113,7 @@
         <v>82</v>
       </c>
       <c r="H160" t="s" s="2">
-        <v>75</v>
+        <v>152</v>
       </c>
       <c r="I160" t="s" s="2">
         <v>75</v>
@@ -18143,9 +18122,11 @@
         <v>75</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="L160" s="2"/>
+        <v>450</v>
+      </c>
+      <c r="L160" t="s" s="2">
+        <v>451</v>
+      </c>
       <c r="M160" s="2"/>
       <c r="N160" s="2"/>
       <c r="O160" s="2"/>
@@ -18196,7 +18177,7 @@
         <v>75</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>81</v>
@@ -18216,21 +18197,23 @@
     </row>
     <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E161" s="2"/>
+      <c r="E161" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F161" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G161" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H161" t="s" s="2">
         <v>75</v>
@@ -18242,10 +18225,12 @@
         <v>75</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>451</v>
+        <v>86</v>
       </c>
       <c r="L161" s="2"/>
-      <c r="M161" s="2"/>
+      <c r="M161" t="s" s="2">
+        <v>87</v>
+      </c>
       <c r="N161" s="2"/>
       <c r="O161" s="2"/>
       <c r="P161" t="s" s="2">
@@ -18271,13 +18256,11 @@
         <v>75</v>
       </c>
       <c r="X161" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y161" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y161" s="2"/>
       <c r="Z161" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA161" t="s" s="2">
         <v>75</v>
@@ -18295,13 +18278,13 @@
         <v>75</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>450</v>
+        <v>90</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH161" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI161" t="s" s="2">
         <v>75</v>
@@ -18313,12 +18296,12 @@
         <v>75</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -18332,7 +18315,7 @@
         <v>82</v>
       </c>
       <c r="H162" t="s" s="2">
-        <v>152</v>
+        <v>75</v>
       </c>
       <c r="I162" t="s" s="2">
         <v>75</v>
@@ -18341,12 +18324,12 @@
         <v>75</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>453</v>
-      </c>
-      <c r="L162" t="s" s="2">
-        <v>454</v>
-      </c>
-      <c r="M162" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="L162" s="2"/>
+      <c r="M162" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="N162" s="2"/>
       <c r="O162" s="2"/>
       <c r="P162" t="s" s="2">
@@ -18396,7 +18379,7 @@
         <v>75</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>452</v>
+        <v>94</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>81</v>
@@ -18416,18 +18399,16 @@
     </row>
     <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E163" t="s" s="2">
-        <v>85</v>
-      </c>
+      <c r="E163" s="2"/>
       <c r="F163" t="s" s="2">
         <v>81</v>
       </c>
@@ -18444,11 +18425,11 @@
         <v>75</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>86</v>
+        <v>96</v>
       </c>
       <c r="L163" s="2"/>
       <c r="M163" t="s" s="2">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="N163" s="2"/>
       <c r="O163" s="2"/>
@@ -18475,11 +18456,13 @@
         <v>75</v>
       </c>
       <c r="X163" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y163" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y163" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z163" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA163" t="s" s="2">
         <v>75</v>
@@ -18497,7 +18480,7 @@
         <v>75</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>81</v>
@@ -18509,7 +18492,7 @@
         <v>75</v>
       </c>
       <c r="AJ163" t="s" s="2">
-        <v>75</v>
+        <v>99</v>
       </c>
       <c r="AK163" t="s" s="2">
         <v>75</v>
@@ -18517,21 +18500,23 @@
     </row>
     <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E164" s="2"/>
+      <c r="E164" t="s" s="2">
+        <v>85</v>
+      </c>
       <c r="F164" t="s" s="2">
         <v>81</v>
       </c>
       <c r="G164" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H164" t="s" s="2">
         <v>75</v>
@@ -18543,11 +18528,11 @@
         <v>75</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="L164" s="2"/>
       <c r="M164" t="s" s="2">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" s="2"/>
@@ -18574,13 +18559,11 @@
         <v>75</v>
       </c>
       <c r="X164" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y164" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y164" s="2"/>
       <c r="Z164" t="s" s="2">
-        <v>75</v>
+        <v>89</v>
       </c>
       <c r="AA164" t="s" s="2">
         <v>75</v>
@@ -18598,13 +18581,13 @@
         <v>75</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH164" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI164" t="s" s="2">
         <v>75</v>
@@ -18618,16 +18601,18 @@
     </row>
     <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E165" s="2"/>
+      <c r="E165" t="s" s="2">
+        <v>102</v>
+      </c>
       <c r="F165" t="s" s="2">
         <v>81</v>
       </c>
@@ -18644,11 +18629,11 @@
         <v>75</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="L165" s="2"/>
       <c r="M165" t="s" s="2">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="N165" s="2"/>
       <c r="O165" s="2"/>
@@ -18699,7 +18684,7 @@
         <v>75</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>81</v>
@@ -18711,7 +18696,7 @@
         <v>75</v>
       </c>
       <c r="AJ165" t="s" s="2">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="AK165" t="s" s="2">
         <v>75</v>
@@ -18719,17 +18704,17 @@
     </row>
     <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E166" t="s" s="2">
-        <v>85</v>
+        <v>107</v>
       </c>
       <c r="F166" t="s" s="2">
         <v>81</v>
@@ -18747,11 +18732,11 @@
         <v>75</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="L166" s="2"/>
       <c r="M166" t="s" s="2">
-        <v>87</v>
+        <v>109</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" s="2"/>
@@ -18778,11 +18763,13 @@
         <v>75</v>
       </c>
       <c r="X166" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y166" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y166" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z166" t="s" s="2">
-        <v>89</v>
+        <v>75</v>
       </c>
       <c r="AA166" t="s" s="2">
         <v>75</v>
@@ -18800,7 +18787,7 @@
         <v>75</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>81</v>
@@ -18820,20 +18807,20 @@
     </row>
     <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E167" t="s" s="2">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="F167" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G167" t="s" s="2">
         <v>76</v>
@@ -18848,11 +18835,11 @@
         <v>75</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="L167" s="2"/>
       <c r="M167" t="s" s="2">
-        <v>104</v>
+        <v>114</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" s="2"/>
@@ -18861,7 +18848,7 @@
       </c>
       <c r="Q167" s="2"/>
       <c r="R167" t="s" s="2">
-        <v>75</v>
+        <v>115</v>
       </c>
       <c r="S167" t="s" s="2">
         <v>75</v>
@@ -18903,7 +18890,7 @@
         <v>75</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>81</v>
@@ -18923,20 +18910,20 @@
     </row>
     <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
         <v>75</v>
       </c>
       <c r="E168" t="s" s="2">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="F168" t="s" s="2">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="G168" t="s" s="2">
         <v>76</v>
@@ -18951,11 +18938,11 @@
         <v>75</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="L168" s="2"/>
       <c r="M168" t="s" s="2">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -19006,7 +18993,7 @@
         <v>75</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>81</v>
@@ -19026,23 +19013,21 @@
     </row>
     <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E169" t="s" s="2">
-        <v>112</v>
-      </c>
+      <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G169" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H169" t="s" s="2">
         <v>75</v>
@@ -19054,11 +19039,11 @@
         <v>75</v>
       </c>
       <c r="K169" t="s" s="2">
-        <v>113</v>
+        <v>96</v>
       </c>
       <c r="L169" s="2"/>
       <c r="M169" t="s" s="2">
-        <v>114</v>
+        <v>123</v>
       </c>
       <c r="N169" s="2"/>
       <c r="O169" s="2"/>
@@ -19067,7 +19052,7 @@
       </c>
       <c r="Q169" s="2"/>
       <c r="R169" t="s" s="2">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="S169" t="s" s="2">
         <v>75</v>
@@ -19109,13 +19094,13 @@
         <v>75</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH169" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI169" t="s" s="2">
         <v>75</v>
@@ -19129,20 +19114,18 @@
     </row>
     <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
         <v>75</v>
       </c>
-      <c r="E170" t="s" s="2">
-        <v>118</v>
-      </c>
+      <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="G170" t="s" s="2">
         <v>76</v>
@@ -19157,23 +19140,21 @@
         <v>75</v>
       </c>
       <c r="K170" t="s" s="2">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="L170" s="2"/>
-      <c r="M170" t="s" s="2">
-        <v>119</v>
-      </c>
+      <c r="M170" s="2"/>
       <c r="N170" s="2"/>
       <c r="O170" s="2"/>
       <c r="P170" t="s" s="2">
-        <v>75</v>
+        <v>462</v>
       </c>
       <c r="Q170" s="2"/>
       <c r="R170" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S170" t="s" s="2">
-        <v>75</v>
+        <v>462</v>
       </c>
       <c r="T170" t="s" s="2">
         <v>75</v>
@@ -19188,13 +19169,11 @@
         <v>75</v>
       </c>
       <c r="X170" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y170" t="s" s="2">
-        <v>75</v>
-      </c>
+        <v>88</v>
+      </c>
+      <c r="Y170" s="2"/>
       <c r="Z170" t="s" s="2">
-        <v>75</v>
+        <v>463</v>
       </c>
       <c r="AA170" t="s" s="2">
         <v>75</v>
@@ -19212,7 +19191,7 @@
         <v>75</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>120</v>
+        <v>464</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>81</v>
@@ -19232,10 +19211,10 @@
     </row>
     <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -19246,7 +19225,7 @@
         <v>81</v>
       </c>
       <c r="G171" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H171" t="s" s="2">
         <v>75</v>
@@ -19258,12 +19237,10 @@
         <v>75</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>96</v>
+        <v>108</v>
       </c>
       <c r="L171" s="2"/>
-      <c r="M171" t="s" s="2">
-        <v>123</v>
-      </c>
+      <c r="M171" s="2"/>
       <c r="N171" s="2"/>
       <c r="O171" s="2"/>
       <c r="P171" t="s" s="2">
@@ -19271,7 +19248,7 @@
       </c>
       <c r="Q171" s="2"/>
       <c r="R171" t="s" s="2">
-        <v>75</v>
+        <v>466</v>
       </c>
       <c r="S171" t="s" s="2">
         <v>75</v>
@@ -19313,13 +19290,13 @@
         <v>75</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>126</v>
+        <v>467</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>81</v>
       </c>
       <c r="AH171" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI171" t="s" s="2">
         <v>75</v>
@@ -19333,10 +19310,10 @@
     </row>
     <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -19359,21 +19336,21 @@
         <v>75</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>86</v>
+        <v>469</v>
       </c>
       <c r="L172" s="2"/>
       <c r="M172" s="2"/>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
       <c r="P172" t="s" s="2">
-        <v>465</v>
+        <v>75</v>
       </c>
       <c r="Q172" s="2"/>
       <c r="R172" t="s" s="2">
         <v>75</v>
       </c>
       <c r="S172" t="s" s="2">
-        <v>465</v>
+        <v>75</v>
       </c>
       <c r="T172" t="s" s="2">
         <v>75</v>
@@ -19388,11 +19365,13 @@
         <v>75</v>
       </c>
       <c r="X172" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="Y172" s="2"/>
+        <v>75</v>
+      </c>
+      <c r="Y172" t="s" s="2">
+        <v>75</v>
+      </c>
       <c r="Z172" t="s" s="2">
-        <v>466</v>
+        <v>75</v>
       </c>
       <c r="AA172" t="s" s="2">
         <v>75</v>
@@ -19410,7 +19389,7 @@
         <v>75</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>81</v>
@@ -19430,10 +19409,10 @@
     </row>
     <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -19456,7 +19435,7 @@
         <v>75</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>108</v>
+        <v>469</v>
       </c>
       <c r="L173" s="2"/>
       <c r="M173" s="2"/>
@@ -19467,7 +19446,7 @@
       </c>
       <c r="Q173" s="2"/>
       <c r="R173" t="s" s="2">
-        <v>469</v>
+        <v>75</v>
       </c>
       <c r="S173" t="s" s="2">
         <v>75</v>
@@ -19509,7 +19488,7 @@
         <v>75</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>81</v>
@@ -19529,10 +19508,10 @@
     </row>
     <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -19555,7 +19534,7 @@
         <v>75</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L174" s="2"/>
       <c r="M174" s="2"/>
@@ -19608,7 +19587,7 @@
         <v>75</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>81</v>
@@ -19628,10 +19607,10 @@
     </row>
     <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -19654,9 +19633,11 @@
         <v>75</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>472</v>
-      </c>
-      <c r="L175" s="2"/>
+        <v>477</v>
+      </c>
+      <c r="L175" t="s" s="2">
+        <v>478</v>
+      </c>
       <c r="M175" s="2"/>
       <c r="N175" s="2"/>
       <c r="O175" s="2"/>
@@ -19707,7 +19688,7 @@
         <v>75</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>81</v>
@@ -19727,10 +19708,10 @@
     </row>
     <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
@@ -19753,7 +19734,7 @@
         <v>75</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="L176" s="2"/>
       <c r="M176" s="2"/>
@@ -19806,7 +19787,7 @@
         <v>75</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>81</v>
@@ -19826,10 +19807,10 @@
     </row>
     <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -19852,10 +19833,10 @@
         <v>75</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="M177" s="2"/>
       <c r="N177" s="2"/>
@@ -19907,7 +19888,7 @@
         <v>75</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>81</v>
@@ -19927,10 +19908,10 @@
     </row>
     <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -19953,9 +19934,11 @@
         <v>75</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>484</v>
-      </c>
-      <c r="L178" s="2"/>
+        <v>488</v>
+      </c>
+      <c r="L178" t="s" s="2">
+        <v>489</v>
+      </c>
       <c r="M178" s="2"/>
       <c r="N178" s="2"/>
       <c r="O178" s="2"/>
@@ -20006,7 +19989,7 @@
         <v>75</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>485</v>
+        <v>490</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>81</v>
@@ -20026,10 +20009,10 @@
     </row>
     <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>486</v>
+        <v>491</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -20052,10 +20035,10 @@
         <v>75</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>487</v>
+        <v>492</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>488</v>
+        <v>493</v>
       </c>
       <c r="M179" s="2"/>
       <c r="N179" s="2"/>
@@ -20107,7 +20090,7 @@
         <v>75</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>489</v>
+        <v>494</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>81</v>
@@ -20127,10 +20110,10 @@
     </row>
     <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>490</v>
+        <v>495</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -20153,11 +20136,9 @@
         <v>75</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>491</v>
-      </c>
-      <c r="L180" t="s" s="2">
-        <v>492</v>
-      </c>
+        <v>496</v>
+      </c>
+      <c r="L180" s="2"/>
       <c r="M180" s="2"/>
       <c r="N180" s="2"/>
       <c r="O180" s="2"/>
@@ -20208,7 +20189,7 @@
         <v>75</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>81</v>
@@ -20228,10 +20209,10 @@
     </row>
     <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -20254,11 +20235,9 @@
         <v>75</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>495</v>
-      </c>
-      <c r="L181" t="s" s="2">
-        <v>496</v>
-      </c>
+        <v>499</v>
+      </c>
+      <c r="L181" s="2"/>
       <c r="M181" s="2"/>
       <c r="N181" s="2"/>
       <c r="O181" s="2"/>
@@ -20309,7 +20288,7 @@
         <v>75</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>81</v>
@@ -20329,10 +20308,10 @@
     </row>
     <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -20355,7 +20334,7 @@
         <v>75</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="L182" s="2"/>
       <c r="M182" s="2"/>
@@ -20408,7 +20387,7 @@
         <v>75</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>81</v>
@@ -20428,10 +20407,10 @@
     </row>
     <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -20454,7 +20433,7 @@
         <v>75</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="L183" s="2"/>
       <c r="M183" s="2"/>
@@ -20507,7 +20486,7 @@
         <v>75</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>81</v>
@@ -20522,209 +20501,11 @@
         <v>75</v>
       </c>
       <c r="AK183" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="184" hidden="true">
-      <c r="A184" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="B184" t="s" s="2">
-        <v>504</v>
-      </c>
-      <c r="C184" s="2"/>
-      <c r="D184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E184" s="2"/>
-      <c r="F184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G184" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K184" t="s" s="2">
-        <v>505</v>
-      </c>
-      <c r="L184" s="2"/>
-      <c r="M184" s="2"/>
-      <c r="N184" s="2"/>
-      <c r="O184" s="2"/>
-      <c r="P184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q184" s="2"/>
-      <c r="R184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF184" t="s" s="2">
-        <v>506</v>
-      </c>
-      <c r="AG184" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH184" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ184" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK184" t="s" s="2">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="185" hidden="true">
-      <c r="A185" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="B185" t="s" s="2">
-        <v>507</v>
-      </c>
-      <c r="C185" s="2"/>
-      <c r="D185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="E185" s="2"/>
-      <c r="F185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="G185" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="I185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="J185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="K185" t="s" s="2">
-        <v>508</v>
-      </c>
-      <c r="L185" s="2"/>
-      <c r="M185" s="2"/>
-      <c r="N185" s="2"/>
-      <c r="O185" s="2"/>
-      <c r="P185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Q185" s="2"/>
-      <c r="R185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="S185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="T185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="U185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="V185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="W185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="X185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Y185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="Z185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AA185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AB185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AC185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AD185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AE185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AF185" t="s" s="2">
-        <v>509</v>
-      </c>
-      <c r="AG185" t="s" s="2">
-        <v>81</v>
-      </c>
-      <c r="AH185" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AJ185" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AK185" t="s" s="2">
         <v>75</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AK185">
+  <autoFilter ref="A1:AK183">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -20734,7 +20515,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI184">
+  <conditionalFormatting sqref="A2:AI182">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5749" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5751" uniqueCount="507">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T08:06:17+00:00</t>
+    <t>2026-10-08T10:07:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1096,10 +1096,10 @@
     <t>Organizer.participant.typeCode</t>
   </si>
   <si>
+    <t>Code issu du JDV_HL7_v3_ParticipationType_CISIS (2.16.840.1.113883.1.11.10901).</t>
+  </si>
+  <si>
     <t>RESP</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ParticipationType-cisis|20260916095457</t>
   </si>
   <si>
     <t>Participant2.typeCode</t>
@@ -1930,7 +1930,7 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="73.28515625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="72.671875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
@@ -13054,7 +13054,9 @@
       <c r="K110" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L110" s="2"/>
+      <c r="L110" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="M110" s="2"/>
       <c r="N110" s="2"/>
       <c r="O110" s="2"/>
@@ -13066,7 +13068,7 @@
         <v>75</v>
       </c>
       <c r="S110" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="T110" t="s" s="2">
         <v>75</v>
@@ -13085,7 +13087,7 @@
       </c>
       <c r="Y110" s="2"/>
       <c r="Z110" t="s" s="2">
-        <v>350</v>
+        <v>233</v>
       </c>
       <c r="AA110" t="s" s="2">
         <v>75</v>
@@ -16516,7 +16518,9 @@
       <c r="K144" t="s" s="2">
         <v>86</v>
       </c>
-      <c r="L144" s="2"/>
+      <c r="L144" t="s" s="2">
+        <v>349</v>
+      </c>
       <c r="M144" s="2"/>
       <c r="N144" s="2"/>
       <c r="O144" s="2"/>
@@ -16547,7 +16551,7 @@
       </c>
       <c r="Y144" s="2"/>
       <c r="Z144" t="s" s="2">
-        <v>350</v>
+        <v>233</v>
       </c>
       <c r="AA144" t="s" s="2">
         <v>75</v>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T10:07:19+00:00</t>
+    <t>2026-10-08T14:58:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-08T14:58:47+00:00</t>
+    <t>2026-10-12T13:25:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fix/slicing-type-this/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
+++ b/fix/slicing-type-this/ig/StructureDefinition-fr-cda-isolat-microbiologique.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-12T13:25:25+00:00</t>
+    <t>2026-10-14T12:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
